--- a/documents_new/4. WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents_new/4. WeValue_현장ACD_메신저템플릿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\임덕수\2026-QI\documents_new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lds85\Desktop\임덕수\git\2026-QI\documents_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0B7A9D-9E24-4B3E-A7AF-3B39F79DF353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1B83D0-08A1-44A2-8762-A19E3645E3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8670" yWindow="1440" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="병동간호사" sheetId="5" r:id="rId1"/>
@@ -921,7 +921,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -965,6 +965,102 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -974,122 +1070,23 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1482,375 +1479,378 @@
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
     </row>
     <row r="4" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="18">
         <v>131</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="24"/>
-      <c r="L4" s="25" t="str">
+      <c r="K4" s="19"/>
+      <c r="L4" s="20" t="str">
         <f>"["&amp;D4&amp;"/"&amp;F4&amp;"/"&amp;H4&amp;"] "&amp;J4</f>
         <v>[131/A/데이] 이미자</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="21" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="28"/>
-    </row>
-    <row r="6" spans="1:12" s="21" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="53" t="s">
+    <row r="5" spans="1:12" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="15"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="23"/>
+    </row>
+    <row r="6" spans="1:12" s="16" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15"/>
+      <c r="B6" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="28"/>
-    </row>
-    <row r="7" spans="1:12" s="21" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="28"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="15"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="23"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="29" t="s">
+      <c r="F8" s="39"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="24" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="31">
+      <c r="B9" s="25">
         <v>1411</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <v>123456</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="47" t="str">
+      <c r="F9" s="39"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="37" t="str">
         <f ca="1">"["&amp;B9&amp;"]-["&amp;C9&amp;"]-["&amp;D9&amp;"]-["&amp;E9&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
-        <v>[1411]-[123456]-[나환자]-[배상병]-[0405]-[1447]</v>
+        <v>[1411]-[123456]-[나환자]-[배상병]-[0409]-[2036]</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="29" t="s">
+      <c r="F11" s="51"/>
+      <c r="G11" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="J11" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L11" s="24" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="27">
         <v>10</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35" t="s">
+      <c r="F12" s="45"/>
+      <c r="G12" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="36" t="str">
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="29" t="str">
         <f ca="1">C12&amp;IF($L$9="","", "[A]"&amp;$L$9&amp;" / "&amp;E12&amp;" / 요청:"&amp;G12&amp;" / "&amp;D12)</f>
-        <v>[CVR][A][1411]-[123456]-[나환자]-[배상병]-[0405]-[1447] / 38.8/ANC:500 / 요청:해열제. GFS.항생제 / 10</v>
+        <v>[CVR][A][1411]-[123456]-[나환자]-[배상병]-[0409]-[2036] / 38.8/ANC:500 / 요청:해열제. GFS.항생제 / 10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="36" t="str">
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="29" t="str">
         <f ca="1">C13&amp;IF($L$9="","", "[A]"&amp;$L$9&amp;" / "&amp;E13&amp;" / 요청:"&amp;G13&amp;" / "&amp;D13)</f>
-        <v xml:space="preserve">[A][1411]-[123456]-[나환자]-[배상병]-[0405]-[1447] /  / 요청: / </v>
+        <v xml:space="preserve">[A][1411]-[123456]-[나환자]-[배상병]-[0409]-[2036] /  / 요청: / </v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="36" t="str">
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="29" t="str">
         <f ca="1">IF($L$9="","", "[C]"&amp;$L$9&amp;" / "&amp;IF(H14="","{사유코드}",H14)&amp;" / 다음확인 "&amp;I14&amp;" (전화 1회 후)")</f>
-        <v>[C][1411]-[123456]-[나환자]-[배상병]-[0405]-[1447] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1411]-[123456]-[나환자]-[배상병]-[0409]-[2036] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="36" t="str">
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="29" t="str">
         <f ca="1">IF($L$9="","", "(보고)"&amp;$L$9&amp;"/"&amp;E15&amp;IF(E15="","","/")&amp;"12")</f>
-        <v>(보고)[1411]-[123456]-[나환자]-[배상병]-[0405]-[1447]/12</v>
+        <v>(보고)[1411]-[123456]-[나환자]-[배상병]-[0409]-[2036]/12</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="46"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="36"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="37"/>
-      <c r="E17" s="30" t="s">
+      <c r="D17" s="53"/>
+      <c r="E17" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30" t="s">
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="29"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="24"/>
     </row>
     <row r="18" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39" t="s">
+      <c r="D18" s="52"/>
+      <c r="E18" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39" t="s">
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="39"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="36" t="str">
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="29" t="str">
         <f ca="1">IF($L$9="","", "[A][야간이음기록]"&amp;$L$9&amp;"/지금:"&amp;C18&amp;"/조치:"&amp;E18&amp;"/[D]"&amp;E18&amp;I18)</f>
-        <v>[A][야간이음기록][1411]-[123456]-[나환자]-[배상병]-[0405]-[1447]/지금:4월5일 새벽2시경 튜브막히면서 sat저하.호흡곤란/조치:튜브변경, 개방성유지.내관소독.디솔린투여,HF 연결/[D]튜브변경, 개방성유지.내관소독.디솔린투여,HF 연결튜브개방성유지.sat100%</v>
+        <v>[A][야간이음기록][1411]-[123456]-[나환자]-[배상병]-[0409]-[2036]/지금:4월5일 새벽2시경 튜브막히면서 sat저하.호흡곤란/조치:튜브변경, 개방성유지.내관소독.디솔린투여,HF 연결/[D]튜브변경, 개방성유지.내관소독.디솔린투여,HF 연결튜브개방성유지.sat100%</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:L3"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:H18"/>
     <mergeCell ref="I18:K18"/>
@@ -1861,9 +1861,6 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C12:D13">
@@ -1961,289 +1958,289 @@
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
     </row>
     <row r="4" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="56" t="s">
+      <c r="J4" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="K4" s="24"/>
-      <c r="L4" s="25" t="str">
+      <c r="K4" s="19"/>
+      <c r="L4" s="20" t="str">
         <f>"["&amp;D4&amp;"/"&amp;F4&amp;"] "&amp;H4&amp;"("&amp;J4&amp;")"</f>
         <v>[131-ENT/박재홍] 이미자(데이)</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
     </row>
     <row r="6" spans="1:12" s="14" customFormat="1" ht="90.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="26"/>
-    </row>
-    <row r="7" spans="1:12" s="21" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="28"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="21"/>
+    </row>
+    <row r="7" spans="1:12" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="15"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="23"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="29" t="s">
+      <c r="F8" s="39"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="24" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="31">
+      <c r="B9" s="25">
         <v>1411</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <v>123456</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="47" t="str">
+      <c r="F9" s="39"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="37" t="str">
         <f ca="1">"["&amp;B9&amp;"]-["&amp;C9&amp;"]-["&amp;D9&amp;"]-["&amp;E9&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
-        <v>[1411]-[123456]-[나환자]-[배상병]-[0405]-[1447]</v>
+        <v>[1411]-[123456]-[나환자]-[배상병]-[0409]-[2036]</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="41"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="29" t="s">
+      <c r="F11" s="51"/>
+      <c r="G11" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="29" t="s">
+      <c r="J11" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K11" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L11" s="24" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="36" t="str">
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="29" t="str">
         <f ca="1">C12&amp;IF($L$9="","", "[A]"&amp;$L$9&amp;" / "&amp;E12&amp;" / 요청:"&amp;G12&amp;" / "&amp;D12)</f>
-        <v xml:space="preserve">[A][1411]-[123456]-[나환자]-[배상병]-[0405]-[1447] /  / 요청: / </v>
+        <v xml:space="preserve">[A][1411]-[123456]-[나환자]-[배상병]-[0409]-[2036] /  / 요청: / </v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="36" t="str">
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="29" t="str">
         <f ca="1">IF($L$9="","", "[C]"&amp;$L$9&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
-        <v>[C][1411]-[123456]-[나환자]-[배상병]-[0405]-[1447] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1411]-[123456]-[나환자]-[배상병]-[0409]-[2036] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="33" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="35" t="s">
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="K14" s="35" t="s">
+      <c r="K14" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="L14" s="36" t="str">
+      <c r="L14" s="29" t="str">
         <f ca="1">IF($L$9="","", "[D]"&amp;$L$9&amp;" / 결과:"&amp;E14&amp;" / 현재:"&amp;J14&amp;" / F/U:"&amp;K14)</f>
-        <v>[D][1411]-[123456]-[나환자]-[배상병]-[0405]-[1447] / 결과:발열없음 / 현재:약물유지 / F/U:내일 ANC:500미만시 재투여 :GFS</v>
+        <v>[D][1411]-[123456]-[나환자]-[배상병]-[0409]-[2036] / 결과:발열없음 / 현재:약물유지 / F/U:내일 ANC:500미만시 재투여 :GFS</v>
       </c>
     </row>
   </sheetData>
@@ -2365,11 +2362,11 @@
       <c r="D2" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
       <c r="J2" s="5" t="s">
         <v>30</v>
       </c>
@@ -2388,9 +2385,9 @@
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
       <c r="J3" s="5" t="s">
         <v>31</v>
       </c>
@@ -2409,9 +2406,9 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
       <c r="J4" s="5" t="s">
         <v>32</v>
       </c>

--- a/documents_new/4. WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents_new/4. WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0BC48A-B9D0-407F-BC1D-C7A339285183}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9739DF-2DC6-4D98-A4C5-F087E23DDCEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8670" yWindow="1440" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="병동간호사" sheetId="5" r:id="rId1"/>
     <sheet name="PA" sheetId="2" r:id="rId2"/>
-    <sheet name="02_코드목록" sheetId="3" r:id="rId3"/>
+    <sheet name="02_코드목록" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="142">
   <si>
     <t>D(완료)</t>
   </si>
@@ -319,37 +319,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>WeValue 현장ACD 메신저 템플릿 ( v1.260405 )</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>131-ENT</t>
-  </si>
-  <si>
-    <t>박재홍</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이미자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>데이</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>4월5일 새벽2시경 튜브막히면서 sat저하.호흡곤란</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>튜브변경, 개방성유지.내관소독.디솔린투여,HF 연결</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>튜브개방성유지.sat100%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>약물유지</t>
@@ -378,9 +348,6 @@
     <t>상태변화</t>
   </si>
   <si>
-    <t>퇴원</t>
-  </si>
-  <si>
     <t>수술전/후</t>
   </si>
   <si>
@@ -440,14 +407,6 @@
   </si>
   <si>
     <t>야간 상황</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>38.8/ANC:500/항생제 처방</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>복통 진통제 변비 약ㅊ방</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -516,12 +475,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>배OO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>김OO</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>A팀</t>
@@ -549,6 +503,10 @@
   </si>
   <si>
     <t>이브닝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>김OO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -562,6 +520,29 @@
   </si>
   <si>
     <t>환자 등록번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>박재홍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>식사진행</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>이OO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeValue 현장ACD 메신저 템플릿 ( v1.260414 )</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -574,7 +555,7 @@
     <numFmt numFmtId="177" formatCode="hhmm"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -674,6 +655,14 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -836,7 +825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1050,6 +1039,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1439,7 +1431,7 @@
     <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="48" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="C1" s="48"/>
       <c r="D1" s="49"/>
@@ -1452,21 +1444,21 @@
       <c r="K1" s="49"/>
       <c r="L1" s="49"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -1493,30 +1485,30 @@
         <v>49</v>
       </c>
       <c r="D4" s="18">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>51</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>50</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I4" s="19" t="s">
         <v>80</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="K4" s="19"/>
       <c r="L4" s="20" t="str">
         <f>"["&amp;D4&amp;"/"&amp;F4&amp;"/"&amp;H4&amp;"] "&amp;J4</f>
-        <v>[131/A/데이] 이미자</v>
+        <v>[141/B/데이] 김OO</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
@@ -1551,22 +1543,22 @@
       <c r="A7" s="15"/>
       <c r="B7" s="21"/>
       <c r="C7" s="46" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="G7" s="46" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="22"/>
@@ -1576,14 +1568,26 @@
     <row r="8" spans="1:12" s="16" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
+        <v>130</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="69" t="s">
+        <v>124</v>
+      </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="22"/>
@@ -1594,21 +1598,33 @@
 ■ E (이브닝): "&amp;C9&amp;" (A)"&amp;D9&amp;" (B)"&amp;E9&amp;" (C)"&amp;F9&amp;" (D)"&amp;G9&amp;" (E)"&amp;H9</f>
         <v>[병동]대화방 daily protocol 
 [4월/4일][소속병동 협업방]병동 인력 현황 
-■ D (데이):  (A) (B) (C) (D) (E)
-■ E (이브닝):  (A) (B) (C) (D) (E)</v>
+■ D (데이): 김OO (A)김OO (B)김OO (C)김OO (D)김OO (E)김OO
+■ E (이브닝): 이OO (A)김OO (B)이OO (C)김OO (D)김OO (E)김OO</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="16" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15"/>
       <c r="B9" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
+        <v>131</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="69" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="69" t="s">
+        <v>124</v>
+      </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
@@ -1637,10 +1653,10 @@
         <v>22</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F11" s="39"/>
       <c r="G11" s="1"/>
@@ -1657,9 +1673,15 @@
       <c r="B12" s="25">
         <v>1411</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
+      <c r="C12" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="25">
+        <v>12345</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>137</v>
+      </c>
       <c r="F12" s="39"/>
       <c r="G12" s="38"/>
       <c r="H12" s="38"/>
@@ -1668,7 +1690,7 @@
       <c r="K12" s="41"/>
       <c r="L12" s="37" t="str">
         <f ca="1">"["&amp;B12&amp;"]-["&amp;C12&amp;"]-["&amp;D12&amp;"]-["&amp;E12&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
-        <v>[1411]-[]-[]-[]-[0413]-[2253]</v>
+        <v>[1411]-[박재홍]-[12345]-[이00]-[0414]-[0140]</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1697,7 +1719,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="55" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F14" s="56"/>
       <c r="G14" s="57"/>
@@ -1717,14 +1739,12 @@
         <v>79</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D15" s="27">
         <v>10</v>
       </c>
-      <c r="E15" s="58" t="s">
-        <v>117</v>
-      </c>
+      <c r="E15" s="58"/>
       <c r="F15" s="59"/>
       <c r="G15" s="60"/>
       <c r="H15" s="24"/>
@@ -1733,7 +1753,7 @@
       <c r="K15" s="54"/>
       <c r="L15" s="29" t="str">
         <f ca="1">"["&amp;C15&amp;"/"&amp;D15&amp;"]-"&amp;IF($L$12="","", "[A]"&amp;$L$12&amp;" / "&amp;E15)</f>
-        <v>[CHEMO/10]-[A][1411]-[]-[]-[]-[0413]-[2253] / 38.8/ANC:500/항생제 처방</v>
+        <v xml:space="preserve">[BLOOD/10]-[A][1411]-[박재홍]-[12345]-[이00]-[0414]-[0140] / </v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1742,13 +1762,13 @@
         <v>78</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D16" s="27">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="F16" s="59"/>
       <c r="G16" s="60"/>
@@ -1758,7 +1778,7 @@
       <c r="K16" s="54"/>
       <c r="L16" s="29" t="str">
         <f ca="1">"["&amp;C16&amp;"/"&amp;D16&amp;"]-"&amp;IF($L$12="","", "[A]"&amp;$L$12&amp;"/"&amp;E16)</f>
-        <v>[EMR확인/12]-[A][1411]-[]-[]-[]-[0413]-[2253]/복통 진통제 변비 약ㅊ방</v>
+        <v>[수술전/후/4]-[A][1411]-[박재홍]-[12345]-[이00]-[0414]-[0140]/식사진행</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1771,15 +1791,13 @@
       <c r="E17" s="55"/>
       <c r="F17" s="56"/>
       <c r="G17" s="57"/>
-      <c r="H17" s="27" t="s">
-        <v>9</v>
-      </c>
+      <c r="H17" s="27"/>
       <c r="I17" s="54"/>
       <c r="J17" s="54"/>
       <c r="K17" s="54"/>
       <c r="L17" s="29" t="str">
         <f ca="1">"[C/"&amp;H17&amp;"]"&amp;$L$12</f>
-        <v>[C/인계][1411]-[]-[]-[]-[0413]-[2253]</v>
+        <v>[C/][1411]-[박재홍]-[12345]-[이00]-[0414]-[0140]</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1802,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D19" s="53"/>
       <c r="E19" s="54" t="s">
@@ -1823,24 +1841,18 @@
       <c r="B20" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="52" t="s">
-        <v>87</v>
-      </c>
+      <c r="C20" s="52"/>
       <c r="D20" s="52"/>
-      <c r="E20" s="52" t="s">
-        <v>88</v>
-      </c>
+      <c r="E20" s="52"/>
       <c r="F20" s="52"/>
       <c r="G20" s="52"/>
       <c r="H20" s="52"/>
-      <c r="I20" s="52" t="s">
-        <v>89</v>
-      </c>
+      <c r="I20" s="52"/>
       <c r="J20" s="52"/>
       <c r="K20" s="52"/>
       <c r="L20" s="29" t="str">
         <f ca="1">IF($L$12="","", "[A][야간이음기록]"&amp;$L$12&amp;"/지금:"&amp;C20&amp;"/조치:"&amp;E20&amp;"/[D]"&amp;E20&amp;I20)</f>
-        <v>[A][야간이음기록][1411]-[]-[]-[]-[0413]-[2253]/지금:4월5일 새벽2시경 튜브막히면서 sat저하.호흡곤란/조치:튜브변경, 개방성유지.내관소독.디솔린투여,HF 연결/[D]튜브변경, 개방성유지.내관소독.디솔린투여,HF 연결튜브개방성유지.sat100%</v>
+        <v>[A][야간이음기록][1411]-[박재홍]-[12345]-[이00]-[0414]-[0140]/지금:/조치:/[D]</v>
       </c>
     </row>
   </sheetData>
@@ -1959,7 +1971,7 @@
     <row r="1" spans="1:11" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="48" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="C1" s="48"/>
       <c r="D1" s="49"/>
@@ -2009,30 +2021,22 @@
       <c r="C4" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>82</v>
-      </c>
+      <c r="D4" s="18"/>
       <c r="E4" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="43" t="s">
-        <v>83</v>
-      </c>
+      <c r="F4" s="43"/>
       <c r="G4" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="18" t="s">
-        <v>84</v>
-      </c>
+      <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="44" t="s">
-        <v>85</v>
-      </c>
+      <c r="J4" s="44"/>
       <c r="K4" s="20" t="str">
         <f>"["&amp;D4&amp;"/"&amp;F4&amp;"] "&amp;H4&amp;"("&amp;J4&amp;")"</f>
-        <v>[131-ENT/박재홍] 이미자(데이)</v>
+        <v>[/] ()</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.3">
@@ -2051,14 +2055,14 @@
     <row r="6" spans="1:11" s="14" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
       <c r="B6" s="47" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="66" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F6" s="67"/>
       <c r="G6" s="67"/>
@@ -2081,14 +2085,14 @@
     <row r="7" spans="1:11" s="14" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="47" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="66" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="F7" s="67"/>
       <c r="G7" s="67"/>
@@ -2100,14 +2104,14 @@
     <row r="8" spans="1:11" s="14" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="47" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="66" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F8" s="67"/>
       <c r="G8" s="67"/>
@@ -2154,18 +2158,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="25">
-        <v>1411</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="D11" s="25">
-        <v>123455</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>136</v>
-      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="39"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
@@ -2173,7 +2169,7 @@
       <c r="J11" s="38"/>
       <c r="K11" s="37" t="str">
         <f ca="1">"["&amp;B11&amp;"]-["&amp;C11&amp;"]-["&amp;D11&amp;"]-["&amp;E11&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
-        <v>[1411]-[배OO]-[123455]-[김OO]-[0413]-[2253]</v>
+        <v>[]-[]-[]-[]-[0414]-[0140]</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -2201,7 +2197,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="54" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F13" s="54"/>
       <c r="G13" s="24"/>
@@ -2209,10 +2205,10 @@
         <v>3</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>23</v>
@@ -2223,12 +2219,8 @@
       <c r="B14" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="27">
-        <v>10</v>
-      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
       <c r="E14" s="61"/>
       <c r="F14" s="61"/>
       <c r="G14" s="45"/>
@@ -2237,7 +2229,7 @@
       <c r="J14" s="24"/>
       <c r="K14" s="29" t="str">
         <f ca="1">"["&amp;C14&amp;"/"&amp;D14&amp;"]-"&amp;IF($K$11="","", "[A]"&amp;$K$11&amp;" / "&amp;E14)</f>
-        <v xml:space="preserve">[퇴원/10]-[A][1411]-[배OO]-[123455]-[김OO]-[0413]-[2253] / </v>
+        <v xml:space="preserve">[/]-[A][]-[]-[]-[]-[0414]-[0140] / </v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -2255,7 +2247,7 @@
       <c r="J15" s="24"/>
       <c r="K15" s="29" t="str">
         <f ca="1">IF($K$11="","", "[C]"&amp;$K$11&amp;" / "&amp;IF(H15="","{사유코드}",H15)&amp;" / 다음확인 "&amp;I15&amp;" (전화 1회 후)")</f>
-        <v>[C][1411]-[배OO]-[123455]-[김OO]-[0413]-[2253] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][]-[]-[]-[]-[0414]-[0140] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2271,11 +2263,11 @@
       <c r="H16" s="24"/>
       <c r="I16" s="24"/>
       <c r="J16" s="28" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="K16" s="29" t="str">
         <f ca="1">"[D]"&amp;$K$11&amp;" / 현재:"&amp;J16&amp;"/F/U:"&amp;J16</f>
-        <v>[D][1411]-[배OO]-[123455]-[김OO]-[0413]-[2253] / 현재:약물유지/F/U:약물유지</v>
+        <v>[D][]-[]-[]-[]-[0414]-[0140] / 현재:약물유지/F/U:약물유지</v>
       </c>
     </row>
   </sheetData>
@@ -2309,7 +2301,7 @@
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
@@ -2401,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F2" s="62" t="s">
         <v>36</v>
@@ -2413,7 +2405,7 @@
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>30</v>
@@ -2434,7 +2426,7 @@
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>31</v>
@@ -2455,7 +2447,7 @@
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>37</v>
@@ -2466,7 +2458,7 @@
         <v>9</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>32</v>
@@ -2477,7 +2469,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>33</v>
@@ -2488,7 +2480,7 @@
         <v>11</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>34</v>
@@ -2499,7 +2491,7 @@
         <v>12</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>35</v>
@@ -2510,7 +2502,7 @@
         <v>13</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>38</v>
@@ -2521,7 +2513,7 @@
         <v>14</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>39</v>
@@ -2532,7 +2524,7 @@
         <v>15</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="M11" s="4" t="s">
         <v>40</v>
@@ -2563,42 +2555,42 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L16" s="12" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L17" s="12" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L18" s="12" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L19" s="12" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L20" s="12" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L21" s="12" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L22" s="12" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L23" s="12" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="11:12" x14ac:dyDescent="0.3">
@@ -2606,7 +2598,7 @@
         <v>74</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="11:12" x14ac:dyDescent="0.3">
@@ -2616,7 +2608,7 @@
     </row>
     <row r="26" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L26" s="12" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="11:12" x14ac:dyDescent="0.3">
@@ -2629,37 +2621,37 @@
         <v>74</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L29" s="12" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L30" s="12" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L31" s="12" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="11:12" x14ac:dyDescent="0.3">
       <c r="L32" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L33" s="12" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="L34" s="12" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">

--- a/documents_new/4. WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents_new/4. WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9739DF-2DC6-4D98-A4C5-F087E23DDCEA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FABBE1A-4DA3-41A4-A3E4-4398FBE3D4BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8670" yWindow="1440" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="144">
   <si>
     <t>D(완료)</t>
   </si>
@@ -543,6 +543,14 @@
   </si>
   <si>
     <t>WeValue 현장ACD 메신저 템플릿 ( v1.260414 )</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[PA]대화방 Daily protocol </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeValue 현장ACD 메신저 템플릿 ( v1.260415 )</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -555,7 +563,7 @@
     <numFmt numFmtId="177" formatCode="hhmm"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -663,6 +671,12 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="8">
@@ -825,7 +839,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -968,13 +982,31 @@
     <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -986,9 +1018,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1007,41 +1036,38 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1430,51 +1456,51 @@
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
+      <c r="B1" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="54"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
     </row>
     <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
     </row>
     <row r="4" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
@@ -1570,28 +1596,28 @@
       <c r="B8" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="69" t="s">
+      <c r="F8" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="G8" s="69" t="s">
+      <c r="G8" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="50" t="s">
         <v>124</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="22"/>
-      <c r="L8" s="70" t="str">
+      <c r="L8" s="52" t="str">
         <f>"[병동]대화방 daily protocol 
 [4월/4일][소속병동 협업방]병동 인력 현황 
 ■ D (데이): "&amp;C8&amp;" (A)"&amp;D8&amp;" (B)"&amp;E8&amp;" (C)"&amp;F8&amp;" (D)"&amp;G8&amp;" (E)"&amp;H8&amp;"
@@ -1607,28 +1633,28 @@
       <c r="B9" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="E9" s="69" t="s">
+      <c r="E9" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="F9" s="69" t="s">
+      <c r="F9" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="69" t="s">
+      <c r="H9" s="50" t="s">
         <v>124</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
-      <c r="L9" s="71"/>
+      <c r="L9" s="53"/>
     </row>
     <row r="10" spans="1:12" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
@@ -1690,7 +1716,7 @@
       <c r="K12" s="41"/>
       <c r="L12" s="37" t="str">
         <f ca="1">"["&amp;B12&amp;"]-["&amp;C12&amp;"]-["&amp;D12&amp;"]-["&amp;E12&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
-        <v>[1411]-[박재홍]-[12345]-[이00]-[0414]-[0140]</v>
+        <v>[1411]-[박재홍]-[12345]-[이00]-[0415]-[0008]</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1718,17 +1744,17 @@
       <c r="D14" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="55" t="s">
+      <c r="E14" s="60" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="56"/>
-      <c r="G14" s="57"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
       <c r="H14" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="54"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
       <c r="L14" s="24" t="s">
         <v>23</v>
       </c>
@@ -1744,16 +1770,16 @@
       <c r="D15" s="27">
         <v>10</v>
       </c>
-      <c r="E15" s="58"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="60"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="65"/>
       <c r="H15" s="24"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="54"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
       <c r="L15" s="29" t="str">
-        <f ca="1">"["&amp;C15&amp;"/"&amp;D15&amp;"]-"&amp;IF($L$12="","", "[A]"&amp;$L$12&amp;" / "&amp;E15)</f>
-        <v xml:space="preserve">[BLOOD/10]-[A][1411]-[박재홍]-[12345]-[이00]-[0414]-[0140] / </v>
+        <f ca="1">IF(D15=10,"🔴",IF(D15=4,"🟠",IF(D15=12,"🟢","")))&amp;"["&amp;C15&amp;"/"&amp;D15&amp;"]-"&amp;IF($L$12="","", "[A]"&amp;$L$12&amp;" / "&amp;E15)</f>
+        <v xml:space="preserve">🔴[BLOOD/10]-[A][1411]-[박재홍]-[12345]-[이00]-[0415]-[0008] / </v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1765,20 +1791,20 @@
         <v>88</v>
       </c>
       <c r="D16" s="27">
-        <v>4</v>
-      </c>
-      <c r="E16" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="63" t="s">
         <v>138</v>
       </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="60"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="65"/>
       <c r="H16" s="24"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
       <c r="L16" s="29" t="str">
-        <f ca="1">"["&amp;C16&amp;"/"&amp;D16&amp;"]-"&amp;IF($L$12="","", "[A]"&amp;$L$12&amp;"/"&amp;E16)</f>
-        <v>[수술전/후/4]-[A][1411]-[박재홍]-[12345]-[이00]-[0414]-[0140]/식사진행</v>
+        <f ca="1">IF(D16=10,"🔴",IF(D16=4,"🟠",IF(D16=12,"🟢","")))&amp;"["&amp;C16&amp;"/"&amp;D16&amp;"]-"&amp;IF($L$12="","", "[A]"&amp;$L$12&amp;"/"&amp;E16)</f>
+        <v>🟢[수술전/후/12]-[A][1411]-[박재홍]-[12345]-[이00]-[0415]-[0008]/식사진행</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1788,16 +1814,16 @@
       </c>
       <c r="C17" s="24"/>
       <c r="D17" s="24"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="57"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="62"/>
       <c r="H17" s="27"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
       <c r="L17" s="29" t="str">
         <f ca="1">"[C/"&amp;H17&amp;"]"&amp;$L$12</f>
-        <v>[C/][1411]-[박재홍]-[12345]-[이00]-[0414]-[0140]</v>
+        <v>[C/][1411]-[박재홍]-[12345]-[이00]-[0415]-[0008]</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1819,21 +1845,21 @@
       <c r="B19" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="54" t="s">
+      <c r="D19" s="59"/>
+      <c r="E19" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54" t="s">
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="54"/>
-      <c r="K19" s="54"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
       <c r="L19" s="24"/>
     </row>
     <row r="20" spans="1:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1841,34 +1867,34 @@
       <c r="B20" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
       <c r="L20" s="29" t="str">
         <f ca="1">IF($L$12="","", "[A][야간이음기록]"&amp;$L$12&amp;"/지금:"&amp;C20&amp;"/조치:"&amp;E20&amp;"/[D]"&amp;E20&amp;I20)</f>
-        <v>[A][야간이음기록][1411]-[박재홍]-[12345]-[이00]-[0414]-[0140]/지금:/조치:/[D]</v>
+        <v>[A][야간이음기록][1411]-[박재홍]-[12345]-[이00]-[0415]-[0008]/지금:/조치:/[D]</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
     <mergeCell ref="I16:K16"/>
     <mergeCell ref="I17:K17"/>
     <mergeCell ref="L8:L9"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="E16:G16"/>
@@ -1952,7 +1978,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.75" style="13" customWidth="1"/>
@@ -1970,48 +1996,48 @@
   <sheetData>
     <row r="1" spans="1:11" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="57" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
     </row>
     <row r="4" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
@@ -2052,273 +2078,290 @@
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
     </row>
-    <row r="6" spans="1:11" s="14" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" s="14" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="14" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C7" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="66" t="s">
+      <c r="D7" s="70"/>
+      <c r="E7" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="64" t="str">
-        <f>"[PA]대화방 daily protocol 
-[4월/5일][소속과 협업방] PA 업무 개시 및 대응 현황 
-■ 메신저 대표 전담:"&amp;C6&amp;"
- - 휴가/반차: "&amp;C7&amp;"
- - 수술실(OR) : "&amp;C8</f>
-        <v>[PA]대화방 daily protocol 
-[4월/5일][소속과 협업방] PA 업무 개시 및 대응 현황 
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="69" t="str">
+        <f>"[4월/5일][소속과 협업방] PA 업무 개시 및 대응 현황 
+■ 메신저 대표 전담:"&amp;C7&amp;"
+ - 휴가/반차: "&amp;C8&amp;"
+ - 수술실(OR) : "&amp;C9</f>
+        <v>[4월/5일][소속과 협업방] PA 업무 개시 및 대응 현황 
 ■ 메신저 대표 전담:전담 김OO
  - 휴가/반차: 김OO, 박OO
  - 수술실(OR) : 김OO(09:00 ~ 13:00)</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="14" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="66" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="64"/>
-    </row>
     <row r="8" spans="1:11" s="14" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="65"/>
+        <v>117</v>
+      </c>
+      <c r="C8" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="70"/>
       <c r="E8" s="66" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F8" s="67"/>
       <c r="G8" s="67"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="64"/>
-    </row>
-    <row r="9" spans="1:11" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="23"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="24" t="s">
-        <v>24</v>
-      </c>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="69"/>
+    </row>
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
+      <c r="B9" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="70" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="70"/>
+      <c r="E9" s="66" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="69"/>
+    </row>
+    <row r="10" spans="1:11" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="15"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="B11" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>21</v>
+      </c>
       <c r="F11" s="39"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="37" t="str">
-        <f ca="1">"["&amp;B11&amp;"]-["&amp;C11&amp;"]-["&amp;D11&amp;"]-["&amp;E11&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
-        <v>[]-[]-[]-[]-[0414]-[0140]</v>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="24" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-    </row>
-    <row r="13" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="54"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="K13" s="24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="76"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="37" t="str">
+        <f ca="1">"["&amp;B12&amp;"]-["&amp;C12&amp;"]-["&amp;D12&amp;"]-["&amp;E12&amp;"]-["&amp;TEXT(TEXT(NOW(), "mmdd"),"0000")&amp;"]-["&amp;TEXT(TEXT(NOW(), "hhmm"),"0000")&amp;"]"</f>
+        <v>[]-[]-[]-[]-[0415]-[0008]</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+    </row>
+    <row r="14" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="29" t="str">
-        <f ca="1">"["&amp;C14&amp;"/"&amp;D14&amp;"]-"&amp;IF($K$11="","", "[A]"&amp;$K$11&amp;" / "&amp;E14)</f>
-        <v xml:space="preserve">[/]-[A][]-[]-[]-[]-[0414]-[0140] / </v>
+        <v>1</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="51"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="28"/>
+        <v>78</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="27">
+        <v>10</v>
+      </c>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
       <c r="J15" s="24"/>
       <c r="K15" s="29" t="str">
-        <f ca="1">IF($K$11="","", "[C]"&amp;$K$11&amp;" / "&amp;IF(H15="","{사유코드}",H15)&amp;" / 다음확인 "&amp;I15&amp;" (전화 1회 후)")</f>
-        <v>[C][]-[]-[]-[]-[0414]-[0140] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <f ca="1">IF(D15=10,"🔴",IF(D15=4,"🟡",IF(D15=12,"🟢","")))&amp;"["&amp;C15&amp;"/"&amp;D15&amp;"]-"&amp;IF($K$12="","","[A]"&amp;$K$12&amp;" / "&amp;E15)</f>
+        <v xml:space="preserve">🔴[상태변화/10]-[A][]-[]-[]-[]-[0415]-[0008] / </v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="24" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
-      <c r="E16" s="46"/>
+      <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="28" t="s">
+      <c r="H16" s="27"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="29" t="str">
+        <f ca="1">IF($K$12="","", "[C]"&amp;$K$12&amp;" / "&amp;IF(H16="","{사유코드}",H16)&amp;" / 다음확인 "&amp;I16&amp;" (전화 1회 후)")</f>
+        <v>[C][]-[]-[]-[]-[0415]-[0008] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="K16" s="29" t="str">
-        <f ca="1">"[D]"&amp;$K$11&amp;" / 현재:"&amp;J16&amp;"/F/U:"&amp;J16</f>
-        <v>[D][]-[]-[]-[]-[0414]-[0140] / 현재:약물유지/F/U:약물유지</v>
+      <c r="K17" s="29" t="str">
+        <f ca="1">"[D]"&amp;$K$12&amp;" / "&amp;J17</f>
+        <v>[D][]-[]-[]-[]-[0415]-[0008] / 약물유지</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="E6:G6"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="K7:K9"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C14:D14">
+  <conditionalFormatting sqref="C15:D15">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>C14=12</formula>
+      <formula>C15=12</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C14=4</formula>
+      <formula>C15=4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>C14=10</formula>
+      <formula>C15=10</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D14</xm:sqref>
+          <xm:sqref>D15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>H16</xm:sqref>
+          <xm:sqref>H17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D061B27-2ED0-4A89-8EF3-BCF08CD5E27F}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>H15</xm:sqref>
+          <xm:sqref>H16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{33E7ADC8-529F-4927-AAE9-C790AFD91F36}">
           <x14:formula1>
@@ -2330,7 +2373,7 @@
           <x14:formula1>
             <xm:f>'02_코드목록'!$L$16:$L$28</xm:f>
           </x14:formula1>
-          <xm:sqref>C14</xm:sqref>
+          <xm:sqref>C15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A114B589-E418-4F1F-BD4A-0BDAA8E85E85}">
           <x14:formula1>
@@ -2395,11 +2438,11 @@
       <c r="D2" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F2" s="62" t="s">
+      <c r="F2" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
       <c r="J2" s="5" t="s">
         <v>25</v>
       </c>
@@ -2418,9 +2461,9 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
       <c r="J3" s="5" t="s">
         <v>26</v>
       </c>
@@ -2439,9 +2482,9 @@
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
       <c r="J4" s="5" t="s">
         <v>27</v>
       </c>
